--- a/data/source/Ganeinu_Assessments_for_Kriah_Curriculum.xlsx
+++ b/data/source/Ganeinu_Assessments_for_Kriah_Curriculum.xlsx
@@ -477,17 +477,15 @@
         <v xml:space="preserve">Confusing Dagesh_x000d_
 Vav vs Shuruk</v>
       </c>
-      <c r="S2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Confusing Dagesh_x000d_
-Shared Nekudah_x000d_
-dot. Shin /Sin</v>
+      <c r="S2" t="str">
+        <v>Double dotted Shin /Sin Shared dot.</v>
       </c>
       <c r="T2" t="str" xml:space="preserve">
         <v xml:space="preserve">Confusing Dagesh_x000d_
 Vav vs Cholam G2</v>
       </c>
       <c r="U2" t="str">
-        <v>Shared Dot</v>
+        <v>Shared Shin Sin Dot</v>
       </c>
       <c r="V2" t="str" xml:space="preserve">
         <v xml:space="preserve">Kamatz Yud _x000d_
